--- a/marketing/auditorias-seo/revisao-titles-descriptions-h1-2026-09-25.xlsx
+++ b/marketing/auditorias-seo/revisao-titles-descriptions-h1-2026-09-25.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\AppData\Local\Temp\claude\c--Users-franc-solveplan-com-Roberto-Molina---Marketing-1--MKT-Estrategy-3--Agentes-de-IA-ccos-ratos\3fe7c38d-8aa5-4234-b9e2-eb8021efc363\scratchpad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solveplan-my.sharepoint.com/personal/molina_solveplan_com/Documents/publica equipe/projetos/Pre Venda/Comercial/Marketing/1. MKT Estrategy/3. Agentes de IA/ccos-ratos/marketing/auditorias-seo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FE2C9EF-7A5D-48AF-87CA-E04E4A891BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{8FE2C9EF-7A5D-48AF-87CA-E04E4A891BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2265EDB-1BE7-4112-B929-D9DDF6A2E454}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B5D46161-3EB7-4448-AEF2-FB692F6EC46B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{B5D46161-3EB7-4448-AEF2-FB692F6EC46B}"/>
   </bookViews>
   <sheets>
     <sheet name="Como revisar" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="459">
   <si>
     <t>#</t>
   </si>
@@ -1417,6 +1417,9 @@
   </si>
   <si>
     <t>O que NÃO entra nesta etapa: textos novos da home, reescrita da página BDC, alts de imagens e schema. Esses itens vêm nas próximas rodadas.</t>
+  </si>
+  <si>
+    <t>Sim</t>
   </si>
 </sst>
 </file>
@@ -2061,25 +2064,25 @@
   <dimension ref="A1:S81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" customWidth="1"/>
-    <col min="3" max="3" width="40.77734375" customWidth="1"/>
-    <col min="4" max="4" width="20.77734375" customWidth="1"/>
-    <col min="5" max="5" width="38.77734375" customWidth="1"/>
-    <col min="6" max="6" width="6.77734375" customWidth="1"/>
+    <col min="1" max="1" width="4.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="42.77734375" customWidth="1"/>
-    <col min="8" max="8" width="6.77734375" customWidth="1"/>
+    <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="50.77734375" customWidth="1"/>
-    <col min="10" max="10" width="6.77734375" customWidth="1"/>
+    <col min="10" max="10" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="52.77734375" customWidth="1"/>
-    <col min="12" max="12" width="6.77734375" customWidth="1"/>
-    <col min="13" max="13" width="9.77734375" customWidth="1"/>
-    <col min="14" max="14" width="34.77734375" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="34.6640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="40.77734375" customWidth="1"/>
-    <col min="16" max="16" width="12.77734375" customWidth="1"/>
-    <col min="17" max="17" width="34.77734375" customWidth="1"/>
-    <col min="18" max="18" width="12.77734375" customWidth="1"/>
-    <col min="19" max="19" width="34.77734375" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -2193,7 +2196,9 @@
       <c r="Q2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="8"/>
+      <c r="R2" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S2" s="5"/>
     </row>
     <row r="3" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -2248,7 +2253,9 @@
       <c r="Q3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="R3" s="8"/>
+      <c r="R3" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S3" s="5"/>
     </row>
     <row r="4" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -6335,15 +6342,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R81" xr:uid="{A15588D1-AB1D-4AA9-89F9-F2ED57C5FD51}">
-      <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="x12ac">
-          <x12ac:list>"Sim,Não,Ajustar"</x12ac:list>
-        </mc:Choice>
-        <mc:Fallback>
-          <formula1>"Sim,Não,Ajustar"</formula1>
-        </mc:Fallback>
-      </mc:AlternateContent>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R81" xr:uid="{2CC0F8D4-3627-4C2F-8E4D-2D7A82E1C449}">
+      <formula1>"Sim,Não,Ajustar"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/marketing/auditorias-seo/revisao-titles-descriptions-h1-2026-09-25.xlsx
+++ b/marketing/auditorias-seo/revisao-titles-descriptions-h1-2026-09-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solveplan-my.sharepoint.com/personal/molina_solveplan_com/Documents/publica equipe/projetos/Pre Venda/Comercial/Marketing/1. MKT Estrategy/3. Agentes de IA/ccos-ratos/marketing/auditorias-seo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{8FE2C9EF-7A5D-48AF-87CA-E04E4A891BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2265EDB-1BE7-4112-B929-D9DDF6A2E454}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="6_{5609821E-4B17-4700-B784-A6FAD35FC9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{758B1A76-2A3D-4908-B90D-36E45C4F6EFE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{B5D46161-3EB7-4448-AEF2-FB692F6EC46B}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="461">
   <si>
     <t>#</t>
   </si>
@@ -1420,6 +1420,12 @@
   </si>
   <si>
     <t>Sim</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>A pagina não é para publicar, deixa em draft</t>
   </si>
 </sst>
 </file>
@@ -2310,7 +2316,9 @@
       <c r="Q4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="R4" s="8"/>
+      <c r="R4" s="8" t="s">
+        <v>459</v>
+      </c>
       <c r="S4" s="5"/>
     </row>
     <row r="5" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -2359,7 +2367,9 @@
       <c r="Q5" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="R5" s="8"/>
+      <c r="R5" s="8" t="s">
+        <v>459</v>
+      </c>
       <c r="S5" s="5"/>
     </row>
     <row r="6" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -2414,7 +2424,9 @@
       <c r="Q6" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="R6" s="8"/>
+      <c r="R6" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S6" s="5"/>
     </row>
     <row r="7" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -2469,8 +2481,12 @@
       <c r="Q7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="R7" s="8"/>
-      <c r="S7" s="5"/>
+      <c r="R7" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="S7" s="5" t="s">
+        <v>460</v>
+      </c>
     </row>
     <row r="8" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
@@ -2522,7 +2538,9 @@
         <v>26</v>
       </c>
       <c r="Q8" s="3"/>
-      <c r="R8" s="8"/>
+      <c r="R8" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S8" s="5"/>
     </row>
     <row r="9" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -2573,7 +2591,9 @@
         <v>26</v>
       </c>
       <c r="Q9" s="3"/>
-      <c r="R9" s="8"/>
+      <c r="R9" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S9" s="5"/>
     </row>
     <row r="10" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">

--- a/marketing/auditorias-seo/revisao-titles-descriptions-h1-2026-09-25.xlsx
+++ b/marketing/auditorias-seo/revisao-titles-descriptions-h1-2026-09-25.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solveplan-my.sharepoint.com/personal/molina_solveplan_com/Documents/publica equipe/projetos/Pre Venda/Comercial/Marketing/1. MKT Estrategy/3. Agentes de IA/ccos-ratos/marketing/auditorias-seo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\AppData\Local\Temp\claude\c--Users-franc-solveplan-com-Roberto-Molina---Marketing-1--MKT-Estrategy-3--Agentes-de-IA-ccos-ratos\3fe7c38d-8aa5-4234-b9e2-eb8021efc363\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="6_{5609821E-4B17-4700-B784-A6FAD35FC9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{758B1A76-2A3D-4908-B90D-36E45C4F6EFE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A0F359-48CE-40DE-81E0-70BFC46949EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{B5D46161-3EB7-4448-AEF2-FB692F6EC46B}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="461">
   <si>
     <t>#</t>
   </si>
@@ -1422,10 +1422,10 @@
     <t>Sim</t>
   </si>
   <si>
-    <t>Não</t>
-  </si>
-  <si>
     <t>A pagina não é para publicar, deixa em draft</t>
+  </si>
+  <si>
+    <t>Só title e description. H1 fica para o rascunho (muda o visual)</t>
   </si>
 </sst>
 </file>
@@ -2317,9 +2317,11 @@
         <v>42</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="S4" s="5"/>
+        <v>458</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>460</v>
+      </c>
     </row>
     <row r="5" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
@@ -2368,7 +2370,7 @@
         <v>51</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="S5" s="5"/>
     </row>
@@ -2485,7 +2487,7 @@
         <v>458</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -2646,7 +2648,9 @@
         <v>26</v>
       </c>
       <c r="Q10" s="3"/>
-      <c r="R10" s="8"/>
+      <c r="R10" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S10" s="5"/>
     </row>
     <row r="11" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -2701,7 +2705,9 @@
       <c r="Q11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="R11" s="8"/>
+      <c r="R11" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S11" s="5"/>
     </row>
     <row r="12" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -2756,7 +2762,9 @@
       <c r="Q12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="R12" s="8"/>
+      <c r="R12" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S12" s="5"/>
     </row>
     <row r="13" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -2811,7 +2819,9 @@
       <c r="Q13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="R13" s="8"/>
+      <c r="R13" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S13" s="5"/>
     </row>
     <row r="14" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -2864,7 +2874,9 @@
       <c r="Q14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="R14" s="8"/>
+      <c r="R14" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S14" s="5"/>
     </row>
     <row r="15" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -2919,7 +2931,9 @@
       <c r="Q15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="R15" s="8"/>
+      <c r="R15" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S15" s="5"/>
     </row>
     <row r="16" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -2974,7 +2988,9 @@
       <c r="Q16" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="R16" s="8"/>
+      <c r="R16" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S16" s="5"/>
     </row>
     <row r="17" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -3025,7 +3041,9 @@
         <v>50</v>
       </c>
       <c r="Q17" s="3"/>
-      <c r="R17" s="8"/>
+      <c r="R17" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S17" s="5"/>
     </row>
     <row r="18" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -3080,7 +3098,9 @@
       <c r="Q18" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="R18" s="8"/>
+      <c r="R18" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S18" s="5"/>
     </row>
     <row r="19" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -3133,7 +3153,9 @@
         <v>26</v>
       </c>
       <c r="Q19" s="3"/>
-      <c r="R19" s="8"/>
+      <c r="R19" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S19" s="5"/>
     </row>
     <row r="20" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -3184,7 +3206,9 @@
         <v>26</v>
       </c>
       <c r="Q20" s="3"/>
-      <c r="R20" s="8"/>
+      <c r="R20" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S20" s="5"/>
     </row>
     <row r="21" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -3237,7 +3261,9 @@
         <v>26</v>
       </c>
       <c r="Q21" s="3"/>
-      <c r="R21" s="8"/>
+      <c r="R21" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S21" s="5"/>
     </row>
     <row r="22" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -3288,7 +3314,9 @@
         <v>26</v>
       </c>
       <c r="Q22" s="3"/>
-      <c r="R22" s="8"/>
+      <c r="R22" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S22" s="5"/>
     </row>
     <row r="23" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -3339,7 +3367,9 @@
         <v>26</v>
       </c>
       <c r="Q23" s="3"/>
-      <c r="R23" s="8"/>
+      <c r="R23" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="S23" s="5"/>
     </row>
     <row r="24" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">

--- a/marketing/auditorias-seo/revisao-titles-descriptions-h1-2026-09-25.xlsx
+++ b/marketing/auditorias-seo/revisao-titles-descriptions-h1-2026-09-25.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\AppData\Local\Temp\claude\c--Users-franc-solveplan-com-Roberto-Molina---Marketing-1--MKT-Estrategy-3--Agentes-de-IA-ccos-ratos\3fe7c38d-8aa5-4234-b9e2-eb8021efc363\scratchpad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solveplan-my.sharepoint.com/personal/molina_solveplan_com/Documents/publica equipe/projetos/Pre Venda/Comercial/Marketing/1. MKT Estrategy/3. Agentes de IA/ccos-ratos/marketing/auditorias-seo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A0F359-48CE-40DE-81E0-70BFC46949EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{66A0F359-48CE-40DE-81E0-70BFC46949EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7061BB51-9748-40B6-808F-4EF21DFE8C51}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{B5D46161-3EB7-4448-AEF2-FB692F6EC46B}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Revisar e aprovar'!$A$1:$S$81</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="461">
   <si>
     <t>#</t>
   </si>
@@ -552,9 +552,6 @@
     <t>Planejamento de OPEX com SAP Analytics Cloud | Solveplan</t>
   </si>
   <si>
-    <t>Impulsione a eficiência do seu negócio com um planejamento robusto, dinâmico e conectado aos objetivos estratégicos da empresa. A solução de Planejamento de</t>
-  </si>
-  <si>
     <t>Planeje o OPEX de forma dinâmica e conectada à estratégia com SAP Analytics Cloud. Acelerador da Solveplan para despesas operacionais.</t>
   </si>
   <si>
@@ -1426,6 +1423,9 @@
   </si>
   <si>
     <t>Só title e description. H1 fica para o rascunho (muda o visual)</t>
+  </si>
+  <si>
+    <t>Impulsione a eficiência do seu negócio com um planejamento robusto, dinâmico e conectado aos objetivos estratégicos da empresa. A solução de Planejamento de RH</t>
   </si>
 </sst>
 </file>
@@ -1927,12 +1927,12 @@
   <sheetData>
     <row r="1" spans="2:2" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B1" s="11" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
@@ -1940,32 +1940,32 @@
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" s="13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" spans="2:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.3">
@@ -1973,27 +1973,27 @@
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
@@ -2001,22 +2001,22 @@
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.3">
@@ -2024,32 +2024,32 @@
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" s="13" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.3">
@@ -2057,7 +2057,7 @@
     </row>
     <row r="30" spans="2:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -2203,7 +2203,7 @@
         <v>27</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S2" s="5"/>
     </row>
@@ -2260,7 +2260,7 @@
         <v>34</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S3" s="5"/>
     </row>
@@ -2317,10 +2317,10 @@
         <v>42</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -2370,7 +2370,7 @@
         <v>51</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S5" s="5"/>
     </row>
@@ -2427,7 +2427,7 @@
         <v>58</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S6" s="5"/>
     </row>
@@ -2484,10 +2484,10 @@
         <v>65</v>
       </c>
       <c r="R7" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="S7" s="5" t="s">
         <v>458</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="Q8" s="3"/>
       <c r="R8" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S8" s="5"/>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S9" s="5"/>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S10" s="5"/>
     </row>
@@ -2706,7 +2706,7 @@
         <v>90</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S11" s="5"/>
     </row>
@@ -2763,7 +2763,7 @@
         <v>97</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S12" s="5"/>
     </row>
@@ -2820,7 +2820,7 @@
         <v>104</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S13" s="5"/>
     </row>
@@ -2875,7 +2875,7 @@
         <v>110</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S14" s="5"/>
     </row>
@@ -2932,7 +2932,7 @@
         <v>118</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S15" s="5"/>
     </row>
@@ -2989,7 +2989,7 @@
         <v>125</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S16" s="5"/>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S17" s="5"/>
     </row>
@@ -3099,7 +3099,7 @@
         <v>138</v>
       </c>
       <c r="R18" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S18" s="5"/>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="Q19" s="3"/>
       <c r="R19" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S19" s="5"/>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="Q20" s="3"/>
       <c r="R20" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S20" s="5"/>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="Q21" s="3"/>
       <c r="R21" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S21" s="5"/>
     </row>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="Q22" s="3"/>
       <c r="R22" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S22" s="5"/>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="Q23" s="3"/>
       <c r="R23" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S23" s="5"/>
     </row>
@@ -3398,13 +3398,13 @@
         <v>56</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>169</v>
+        <v>460</v>
       </c>
       <c r="J24" s="7">
         <v>156</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L24" s="10">
         <v>134</v>
@@ -3413,7 +3413,7 @@
         <v>23</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>25</v>
@@ -3422,7 +3422,9 @@
         <v>26</v>
       </c>
       <c r="Q24" s="3"/>
-      <c r="R24" s="8"/>
+      <c r="R24" s="8" t="s">
+        <v>457</v>
+      </c>
       <c r="S24" s="5"/>
     </row>
     <row r="25" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -3433,25 +3435,25 @@
         <v>16</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F25" s="9">
         <v>25</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H25" s="10">
         <v>57</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J25" s="7">
         <v>154</v>
@@ -3464,7 +3466,7 @@
         <v>23</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O25" s="3" t="s">
         <v>25</v>
@@ -3473,7 +3475,9 @@
         <v>26</v>
       </c>
       <c r="Q25" s="3"/>
-      <c r="R25" s="8"/>
+      <c r="R25" s="8" t="s">
+        <v>457</v>
+      </c>
       <c r="S25" s="5"/>
     </row>
     <row r="26" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -3484,31 +3488,31 @@
         <v>16</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F26" s="9">
         <v>23</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H26" s="10">
         <v>60</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J26" s="7">
         <v>157</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L26" s="10">
         <v>132</v>
@@ -3517,7 +3521,7 @@
         <v>23</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>25</v>
@@ -3526,7 +3530,9 @@
         <v>26</v>
       </c>
       <c r="Q26" s="3"/>
-      <c r="R26" s="8"/>
+      <c r="R26" s="8" t="s">
+        <v>457</v>
+      </c>
       <c r="S26" s="5"/>
     </row>
     <row r="27" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -3537,31 +3543,31 @@
         <v>16</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F27" s="9">
         <v>22</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H27" s="10">
         <v>52</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J27" s="7">
         <v>156</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L27" s="10">
         <v>132</v>
@@ -3570,7 +3576,7 @@
         <v>23</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>25</v>
@@ -3590,25 +3596,25 @@
         <v>16</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F28" s="9">
         <v>21</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H28" s="10">
         <v>46</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J28" s="7">
         <v>157</v>
@@ -3621,7 +3627,7 @@
         <v>23</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O28" s="3" t="s">
         <v>25</v>
@@ -3641,31 +3647,31 @@
         <v>16</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F29" s="7">
         <v>38</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H29" s="10">
         <v>46</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J29" s="7">
         <v>156</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L29" s="10">
         <v>130</v>
@@ -3674,7 +3680,7 @@
         <v>23</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>25</v>
@@ -3694,13 +3700,13 @@
         <v>16</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="F30" s="7">
         <v>35</v>
@@ -3710,7 +3716,7 @@
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J30" s="7">
         <v>148</v>
@@ -3723,7 +3729,7 @@
         <v>23</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O30" s="3" t="s">
         <v>25</v>
@@ -3732,7 +3738,7 @@
         <v>26</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="R30" s="8"/>
       <c r="S30" s="5"/>
@@ -3745,13 +3751,13 @@
         <v>16</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="F31" s="9">
         <v>25</v>
@@ -3761,7 +3767,7 @@
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J31" s="7">
         <v>149</v>
@@ -3774,7 +3780,7 @@
         <v>23</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O31" s="3" t="s">
         <v>25</v>
@@ -3783,7 +3789,7 @@
         <v>26</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="R31" s="8"/>
       <c r="S31" s="5"/>
@@ -3796,13 +3802,13 @@
         <v>16</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="F32" s="9">
         <v>19</v>
@@ -3812,7 +3818,7 @@
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J32" s="7">
         <v>151</v>
@@ -3825,7 +3831,7 @@
         <v>23</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>25</v>
@@ -3834,7 +3840,7 @@
         <v>26</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="R32" s="8"/>
       <c r="S32" s="5"/>
@@ -3847,13 +3853,13 @@
         <v>16</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>215</v>
       </c>
       <c r="F33" s="7">
         <v>41</v>
@@ -3863,7 +3869,7 @@
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J33" s="7">
         <v>151</v>
@@ -3876,7 +3882,7 @@
         <v>23</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>25</v>
@@ -3885,7 +3891,7 @@
         <v>26</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="R33" s="8"/>
       <c r="S33" s="5"/>
@@ -3895,48 +3901,48 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>221</v>
       </c>
       <c r="F34" s="9">
         <v>25</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J34" s="9">
         <v>14</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L34" s="7"/>
       <c r="M34" s="9" t="s">
         <v>23</v>
       </c>
       <c r="N34" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="O34" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="P34" s="7" t="s">
         <v>50</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R34" s="8"/>
       <c r="S34" s="5"/>
@@ -3946,22 +3952,22 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="F35" s="9">
         <v>20</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H35" s="7"/>
       <c r="I35" s="3"/>
@@ -3969,23 +3975,23 @@
         <v>0</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L35" s="7"/>
       <c r="M35" s="7" t="s">
         <v>47</v>
       </c>
       <c r="N35" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="O35" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="P35" s="7" t="s">
         <v>50</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="R35" s="8"/>
       <c r="S35" s="5"/>
@@ -3995,22 +4001,22 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="F36" s="9">
         <v>20</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H36" s="7"/>
       <c r="I36" s="3"/>
@@ -4018,23 +4024,23 @@
         <v>0</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L36" s="7"/>
       <c r="M36" s="7" t="s">
         <v>47</v>
       </c>
       <c r="N36" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="O36" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="P36" s="7" t="s">
         <v>50</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="R36" s="8"/>
       <c r="S36" s="5"/>
@@ -4044,13 +4050,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>133</v>
@@ -4059,7 +4065,7 @@
         <v>21</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="3"/>
@@ -4067,23 +4073,23 @@
         <v>0</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L37" s="7"/>
       <c r="M37" s="7" t="s">
         <v>47</v>
       </c>
       <c r="N37" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="O37" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="O37" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="P37" s="7" t="s">
         <v>50</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R37" s="8"/>
       <c r="S37" s="5"/>
@@ -4093,22 +4099,22 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>236</v>
       </c>
       <c r="F38" s="9">
         <v>23</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="3"/>
@@ -4116,23 +4122,23 @@
         <v>0</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L38" s="7"/>
       <c r="M38" s="7" t="s">
         <v>47</v>
       </c>
       <c r="N38" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="O38" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="P38" s="7" t="s">
         <v>50</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="R38" s="8"/>
       <c r="S38" s="5"/>
@@ -4142,28 +4148,28 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F39" s="9">
         <v>70</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H39" s="10">
         <v>57</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J39" s="7">
         <v>138</v>
@@ -4176,7 +4182,7 @@
         <v>47</v>
       </c>
       <c r="N39" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O39" s="3" t="s">
         <v>49</v>
@@ -4193,34 +4199,34 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F40" s="9">
         <v>76</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H40" s="10">
         <v>55</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J40" s="9">
         <v>205</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L40" s="10">
         <v>142</v>
@@ -4229,7 +4235,7 @@
         <v>47</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O40" s="3" t="s">
         <v>49</v>
@@ -4246,28 +4252,28 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F41" s="9">
         <v>67</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H41" s="10">
         <v>58</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J41" s="9">
         <v>162</v>
@@ -4280,7 +4286,7 @@
         <v>47</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>49</v>
@@ -4297,28 +4303,28 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F42" s="9">
         <v>94</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H42" s="10">
         <v>54</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J42" s="9">
         <v>167</v>
@@ -4331,7 +4337,7 @@
         <v>47</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>49</v>
@@ -4348,28 +4354,28 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F43" s="9">
         <v>77</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H43" s="10">
         <v>55</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J43" s="9">
         <v>170</v>
@@ -4382,7 +4388,7 @@
         <v>47</v>
       </c>
       <c r="N43" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>49</v>
@@ -4399,28 +4405,28 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F44" s="9">
         <v>72</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H44" s="10">
         <v>56</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J44" s="7">
         <v>158</v>
@@ -4433,7 +4439,7 @@
         <v>47</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>49</v>
@@ -4442,7 +4448,7 @@
         <v>50</v>
       </c>
       <c r="Q44" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="R44" s="8"/>
       <c r="S44" s="5"/>
@@ -4452,28 +4458,28 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F45" s="9">
         <v>81</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H45" s="10">
         <v>54</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J45" s="7">
         <v>137</v>
@@ -4486,7 +4492,7 @@
         <v>47</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>49</v>
@@ -4503,34 +4509,34 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F46" s="9">
         <v>89</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H46" s="10">
         <v>57</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J46" s="9">
         <v>215</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L46" s="10">
         <v>136</v>
@@ -4539,7 +4545,7 @@
         <v>47</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>49</v>
@@ -4556,28 +4562,28 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F47" s="9">
         <v>95</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H47" s="10">
         <v>50</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J47" s="9">
         <v>182</v>
@@ -4590,7 +4596,7 @@
         <v>47</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>49</v>
@@ -4607,28 +4613,28 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F48" s="9">
         <v>77</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H48" s="10">
         <v>55</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J48" s="7">
         <v>158</v>
@@ -4641,7 +4647,7 @@
         <v>47</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>49</v>
@@ -4658,34 +4664,34 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F49" s="9">
         <v>81</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H49" s="10">
         <v>53</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J49" s="9">
         <v>73</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L49" s="10">
         <v>140</v>
@@ -4694,7 +4700,7 @@
         <v>47</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>49</v>
@@ -4711,28 +4717,28 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F50" s="9">
         <v>80</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H50" s="10">
         <v>58</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J50" s="7">
         <v>150</v>
@@ -4745,7 +4751,7 @@
         <v>47</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O50" s="3" t="s">
         <v>49</v>
@@ -4762,28 +4768,28 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F51" s="9">
         <v>75</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H51" s="10">
         <v>50</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J51" s="7">
         <v>149</v>
@@ -4796,7 +4802,7 @@
         <v>47</v>
       </c>
       <c r="N51" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O51" s="3" t="s">
         <v>49</v>
@@ -4813,34 +4819,34 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F52" s="9">
         <v>78</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H52" s="10">
         <v>57</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J52" s="9">
         <v>105</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L52" s="10">
         <v>129</v>
@@ -4849,7 +4855,7 @@
         <v>47</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>49</v>
@@ -4866,28 +4872,28 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F53" s="9">
         <v>81</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H53" s="10">
         <v>52</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J53" s="7">
         <v>154</v>
@@ -4900,7 +4906,7 @@
         <v>47</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O53" s="3" t="s">
         <v>49</v>
@@ -4917,34 +4923,34 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F54" s="9">
         <v>66</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H54" s="10">
         <v>48</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J54" s="9">
         <v>324</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L54" s="10">
         <v>137</v>
@@ -4953,7 +4959,7 @@
         <v>47</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>49</v>
@@ -4970,16 +4976,16 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="E55" s="3" t="s">
         <v>311</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>312</v>
       </c>
       <c r="F55" s="7">
         <v>60</v>
@@ -4989,13 +4995,13 @@
       </c>
       <c r="H55" s="7"/>
       <c r="I55" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J55" s="9">
         <v>255</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L55" s="10">
         <v>136</v>
@@ -5004,7 +5010,7 @@
         <v>47</v>
       </c>
       <c r="N55" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O55" s="3" t="s">
         <v>49</v>
@@ -5013,7 +5019,7 @@
         <v>50</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="R55" s="8"/>
       <c r="S55" s="5"/>
@@ -5023,34 +5029,34 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F56" s="9">
         <v>78</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H56" s="10">
         <v>59</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J56" s="9">
         <v>259</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L56" s="10">
         <v>141</v>
@@ -5059,7 +5065,7 @@
         <v>47</v>
       </c>
       <c r="N56" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O56" s="3" t="s">
         <v>49</v>
@@ -5076,34 +5082,34 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F57" s="9">
         <v>82</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H57" s="10">
         <v>54</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J57" s="9">
         <v>281</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L57" s="10">
         <v>138</v>
@@ -5112,7 +5118,7 @@
         <v>47</v>
       </c>
       <c r="N57" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>49</v>
@@ -5129,28 +5135,28 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F58" s="9">
         <v>90</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H58" s="10">
         <v>53</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J58" s="9">
         <v>192</v>
@@ -5163,7 +5169,7 @@
         <v>47</v>
       </c>
       <c r="N58" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>49</v>
@@ -5172,7 +5178,7 @@
         <v>50</v>
       </c>
       <c r="Q58" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="R58" s="8"/>
       <c r="S58" s="5"/>
@@ -5182,16 +5188,16 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C59" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E59" s="3" t="s">
         <v>331</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>332</v>
       </c>
       <c r="F59" s="9">
         <v>65</v>
@@ -5201,13 +5207,13 @@
       </c>
       <c r="H59" s="7"/>
       <c r="I59" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J59" s="9">
         <v>215</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L59" s="10">
         <v>123</v>
@@ -5216,7 +5222,7 @@
         <v>47</v>
       </c>
       <c r="N59" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>49</v>
@@ -5233,28 +5239,28 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F60" s="9">
         <v>72</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H60" s="10">
         <v>57</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J60" s="7">
         <v>153</v>
@@ -5267,7 +5273,7 @@
         <v>47</v>
       </c>
       <c r="N60" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>49</v>
@@ -5276,7 +5282,7 @@
         <v>50</v>
       </c>
       <c r="Q60" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="R60" s="8"/>
       <c r="S60" s="5"/>
@@ -5286,28 +5292,28 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F61" s="9">
         <v>80</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H61" s="10">
         <v>50</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J61" s="9">
         <v>182</v>
@@ -5320,7 +5326,7 @@
         <v>47</v>
       </c>
       <c r="N61" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O61" s="3" t="s">
         <v>49</v>
@@ -5337,34 +5343,34 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F62" s="9">
         <v>67</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H62" s="10">
         <v>50</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J62" s="9">
         <v>199</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L62" s="10">
         <v>125</v>
@@ -5373,7 +5379,7 @@
         <v>47</v>
       </c>
       <c r="N62" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>49</v>
@@ -5390,34 +5396,34 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F63" s="9">
         <v>79</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H63" s="10">
         <v>51</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J63" s="9">
         <v>182</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L63" s="10">
         <v>137</v>
@@ -5426,7 +5432,7 @@
         <v>47</v>
       </c>
       <c r="N63" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O63" s="3" t="s">
         <v>49</v>
@@ -5435,7 +5441,7 @@
         <v>50</v>
       </c>
       <c r="Q63" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="R63" s="8"/>
       <c r="S63" s="5"/>
@@ -5445,28 +5451,28 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F64" s="9">
         <v>75</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H64" s="10">
         <v>57</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J64" s="7">
         <v>154</v>
@@ -5479,7 +5485,7 @@
         <v>47</v>
       </c>
       <c r="N64" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O64" s="3" t="s">
         <v>49</v>
@@ -5496,28 +5502,28 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F65" s="9">
         <v>76</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H65" s="10">
         <v>58</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J65" s="7">
         <v>151</v>
@@ -5530,7 +5536,7 @@
         <v>47</v>
       </c>
       <c r="N65" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O65" s="3" t="s">
         <v>49</v>
@@ -5547,28 +5553,28 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F66" s="9">
         <v>67</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H66" s="10">
         <v>60</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J66" s="9">
         <v>188</v>
@@ -5581,7 +5587,7 @@
         <v>47</v>
       </c>
       <c r="N66" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>49</v>
@@ -5598,28 +5604,28 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F67" s="9">
         <v>67</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H67" s="10">
         <v>54</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="J67" s="7">
         <v>153</v>
@@ -5632,7 +5638,7 @@
         <v>47</v>
       </c>
       <c r="N67" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O67" s="3" t="s">
         <v>49</v>
@@ -5649,28 +5655,28 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F68" s="9">
         <v>68</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H68" s="10">
         <v>48</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J68" s="7">
         <v>148</v>
@@ -5683,7 +5689,7 @@
         <v>47</v>
       </c>
       <c r="N68" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O68" s="3" t="s">
         <v>49</v>
@@ -5700,34 +5706,34 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F69" s="9">
         <v>91</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H69" s="10">
         <v>53</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J69" s="9">
         <v>193</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L69" s="10">
         <v>141</v>
@@ -5736,7 +5742,7 @@
         <v>47</v>
       </c>
       <c r="N69" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O69" s="3" t="s">
         <v>49</v>
@@ -5753,28 +5759,28 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F70" s="9">
         <v>122</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H70" s="10">
         <v>55</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J70" s="7">
         <v>135</v>
@@ -5787,7 +5793,7 @@
         <v>47</v>
       </c>
       <c r="N70" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O70" s="3" t="s">
         <v>49</v>
@@ -5796,7 +5802,7 @@
         <v>50</v>
       </c>
       <c r="Q70" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="R70" s="8"/>
       <c r="S70" s="5"/>
@@ -5806,34 +5812,34 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F71" s="9">
         <v>82</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H71" s="10">
         <v>58</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J71" s="9">
         <v>180</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L71" s="10">
         <v>134</v>
@@ -5842,7 +5848,7 @@
         <v>47</v>
       </c>
       <c r="N71" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O71" s="3" t="s">
         <v>49</v>
@@ -5859,28 +5865,28 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F72" s="9">
         <v>88</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H72" s="10">
         <v>51</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J72" s="7">
         <v>148</v>
@@ -5893,7 +5899,7 @@
         <v>47</v>
       </c>
       <c r="N72" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>49</v>
@@ -5902,7 +5908,7 @@
         <v>50</v>
       </c>
       <c r="Q72" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="R72" s="8"/>
       <c r="S72" s="5"/>
@@ -5912,28 +5918,28 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F73" s="9">
         <v>114</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H73" s="10">
         <v>50</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J73" s="7">
         <v>154</v>
@@ -5946,7 +5952,7 @@
         <v>47</v>
       </c>
       <c r="N73" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O73" s="3" t="s">
         <v>49</v>
@@ -5963,28 +5969,28 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F74" s="9">
         <v>90</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H74" s="10">
         <v>58</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J74" s="7">
         <v>122</v>
@@ -5997,7 +6003,7 @@
         <v>47</v>
       </c>
       <c r="N74" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O74" s="3" t="s">
         <v>49</v>
@@ -6014,16 +6020,16 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C75" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>401</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>402</v>
       </c>
       <c r="F75" s="7">
         <v>51</v>
@@ -6033,13 +6039,13 @@
       </c>
       <c r="H75" s="7"/>
       <c r="I75" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J75" s="9">
         <v>82</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L75" s="10">
         <v>134</v>
@@ -6048,7 +6054,7 @@
         <v>47</v>
       </c>
       <c r="N75" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O75" s="3" t="s">
         <v>49</v>
@@ -6065,34 +6071,34 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F76" s="9">
         <v>95</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H76" s="10">
         <v>50</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J76" s="9">
         <v>89</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="L76" s="10">
         <v>138</v>
@@ -6101,7 +6107,7 @@
         <v>47</v>
       </c>
       <c r="N76" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>49</v>
@@ -6110,7 +6116,7 @@
         <v>50</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="R76" s="8"/>
       <c r="S76" s="5"/>
@@ -6120,34 +6126,34 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F77" s="9">
         <v>89</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H77" s="10">
         <v>53</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J77" s="9">
         <v>77</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L77" s="10">
         <v>128</v>
@@ -6156,7 +6162,7 @@
         <v>47</v>
       </c>
       <c r="N77" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O77" s="3" t="s">
         <v>49</v>
@@ -6173,16 +6179,16 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C78" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>415</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>416</v>
       </c>
       <c r="F78" s="7">
         <v>38</v>
@@ -6192,13 +6198,13 @@
       </c>
       <c r="H78" s="7"/>
       <c r="I78" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="J78" s="9">
         <v>49</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L78" s="10">
         <v>121</v>
@@ -6207,7 +6213,7 @@
         <v>47</v>
       </c>
       <c r="N78" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O78" s="3" t="s">
         <v>49</v>
@@ -6224,34 +6230,34 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F79" s="9">
         <v>77</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H79" s="10">
         <v>55</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J79" s="9">
         <v>302</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L79" s="10">
         <v>127</v>
@@ -6260,7 +6266,7 @@
         <v>47</v>
       </c>
       <c r="N79" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O79" s="3" t="s">
         <v>49</v>
@@ -6277,34 +6283,34 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F80" s="9">
         <v>87</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H80" s="10">
         <v>48</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J80" s="9">
         <v>303</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L80" s="10">
         <v>127</v>
@@ -6313,7 +6319,7 @@
         <v>47</v>
       </c>
       <c r="N80" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O80" s="3" t="s">
         <v>49</v>
@@ -6330,34 +6336,34 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F81" s="9">
         <v>73</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H81" s="10">
         <v>52</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="J81" s="9">
         <v>214</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L81" s="10">
         <v>132</v>
@@ -6366,7 +6372,7 @@
         <v>47</v>
       </c>
       <c r="N81" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>49</v>

--- a/marketing/auditorias-seo/revisao-titles-descriptions-h1-2026-09-25.xlsx
+++ b/marketing/auditorias-seo/revisao-titles-descriptions-h1-2026-09-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solveplan-my.sharepoint.com/personal/molina_solveplan_com/Documents/publica equipe/projetos/Pre Venda/Comercial/Marketing/1. MKT Estrategy/3. Agentes de IA/ccos-ratos/marketing/auditorias-seo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{66A0F359-48CE-40DE-81E0-70BFC46949EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7061BB51-9748-40B6-808F-4EF21DFE8C51}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="6_{BDBA82EF-C4F1-454E-969C-820D58A5577D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDB42798-EB42-417A-AD2B-3EE58FA4EF94}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{B5D46161-3EB7-4448-AEF2-FB692F6EC46B}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="461">
   <si>
     <t>#</t>
   </si>
@@ -600,9 +600,6 @@
     <t>Planejamento agrícola para grãos com SAP | Solveplan</t>
   </si>
   <si>
-    <t>Com o aumento contínuo no custo dos insumos, a variação nos preços das commodities e a pressão por margens mais saudáveis, o planejamento agrícola deixou de</t>
-  </si>
-  <si>
     <t>Planeje a safra de grãos com SAP Analytics Cloud: custo de insumos, preço de commodities e margens em um só modelo, com a Solveplan.</t>
   </si>
   <si>
@@ -618,9 +615,6 @@
     <t>Dashboards com SAP Analytics Cloud | Solveplan</t>
   </si>
   <si>
-    <t>Ganhe clareza total em tempo real. Com os dashboards da Solveplan, você transforma dados complexos em insights estratégicos, organizando KPIs e relatórios em</t>
-  </si>
-  <si>
     <t>Trocar tag para H1: "DASHBOARDS"</t>
   </si>
   <si>
@@ -1425,7 +1419,13 @@
     <t>Só title e description. H1 fica para o rascunho (muda o visual)</t>
   </si>
   <si>
-    <t>Impulsione a eficiência do seu negócio com um planejamento robusto, dinâmico e conectado aos objetivos estratégicos da empresa. A solução de Planejamento de RH</t>
+    <t>Com o aumento contínuo no custo dos insumos, a variação nos preços das commodities e a pressão por margens mais saudáveis.</t>
+  </si>
+  <si>
+    <t>Impulsione a eficiência do seu negócio com um planejamento robusto, dinâmico e conectado aos objetivos estratégicos da empresa.</t>
+  </si>
+  <si>
+    <t>Ganhe clareza total em tempo real. Com os dashboards da Solveplan, você transforma dados complexos em insights estratégicos, organizando KPIs e relatórios.</t>
   </si>
 </sst>
 </file>
@@ -1927,12 +1927,12 @@
   <sheetData>
     <row r="1" spans="2:2" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B1" s="11" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" s="12" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
@@ -1940,32 +1940,32 @@
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" s="13" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6" spans="2:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.3">
@@ -1973,27 +1973,27 @@
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
@@ -2001,22 +2001,22 @@
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.3">
@@ -2024,32 +2024,32 @@
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" s="13" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.3">
@@ -2057,7 +2057,7 @@
     </row>
     <row r="30" spans="2:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -2203,7 +2203,7 @@
         <v>27</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S2" s="5"/>
     </row>
@@ -2260,7 +2260,7 @@
         <v>34</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S3" s="5"/>
     </row>
@@ -2317,10 +2317,10 @@
         <v>42</v>
       </c>
       <c r="R4" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="S4" s="5" t="s">
         <v>457</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -2370,7 +2370,7 @@
         <v>51</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S5" s="5"/>
     </row>
@@ -2427,7 +2427,7 @@
         <v>58</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S6" s="5"/>
     </row>
@@ -2484,10 +2484,10 @@
         <v>65</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="Q8" s="3"/>
       <c r="R8" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S8" s="5"/>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S9" s="5"/>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S10" s="5"/>
     </row>
@@ -2706,7 +2706,7 @@
         <v>90</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S11" s="5"/>
     </row>
@@ -2763,7 +2763,7 @@
         <v>97</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S12" s="5"/>
     </row>
@@ -2820,7 +2820,7 @@
         <v>104</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S13" s="5"/>
     </row>
@@ -2875,7 +2875,7 @@
         <v>110</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S14" s="5"/>
     </row>
@@ -2932,7 +2932,7 @@
         <v>118</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S15" s="5"/>
     </row>
@@ -2989,7 +2989,7 @@
         <v>125</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S16" s="5"/>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S17" s="5"/>
     </row>
@@ -3099,7 +3099,7 @@
         <v>138</v>
       </c>
       <c r="R18" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S18" s="5"/>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="Q19" s="3"/>
       <c r="R19" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S19" s="5"/>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="Q20" s="3"/>
       <c r="R20" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S20" s="5"/>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="Q21" s="3"/>
       <c r="R21" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S21" s="5"/>
     </row>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="Q22" s="3"/>
       <c r="R22" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S22" s="5"/>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="Q23" s="3"/>
       <c r="R23" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S23" s="5"/>
     </row>
@@ -3398,7 +3398,7 @@
         <v>56</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J24" s="7">
         <v>156</v>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S24" s="5"/>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Q25" s="3"/>
       <c r="R25" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S25" s="5"/>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="Q26" s="3"/>
       <c r="R26" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S26" s="5"/>
     </row>
@@ -3561,13 +3561,13 @@
         <v>52</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>185</v>
+        <v>458</v>
       </c>
       <c r="J27" s="7">
         <v>156</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L27" s="10">
         <v>132</v>
@@ -3576,7 +3576,7 @@
         <v>23</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>25</v>
@@ -3585,7 +3585,9 @@
         <v>26</v>
       </c>
       <c r="Q27" s="3"/>
-      <c r="R27" s="8"/>
+      <c r="R27" s="8" t="s">
+        <v>455</v>
+      </c>
       <c r="S27" s="5"/>
     </row>
     <row r="28" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -3596,25 +3598,25 @@
         <v>16</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F28" s="9">
         <v>21</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H28" s="10">
         <v>46</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>191</v>
+        <v>460</v>
       </c>
       <c r="J28" s="7">
         <v>157</v>
@@ -3627,7 +3629,7 @@
         <v>23</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="O28" s="3" t="s">
         <v>25</v>
@@ -3636,7 +3638,9 @@
         <v>26</v>
       </c>
       <c r="Q28" s="3"/>
-      <c r="R28" s="8"/>
+      <c r="R28" s="8" t="s">
+        <v>455</v>
+      </c>
       <c r="S28" s="5"/>
     </row>
     <row r="29" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -3647,31 +3651,31 @@
         <v>16</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F29" s="7">
         <v>38</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H29" s="10">
         <v>46</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J29" s="7">
         <v>156</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L29" s="10">
         <v>130</v>
@@ -3680,7 +3684,7 @@
         <v>23</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>25</v>
@@ -3700,13 +3704,13 @@
         <v>16</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>201</v>
       </c>
       <c r="F30" s="7">
         <v>35</v>
@@ -3716,7 +3720,7 @@
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J30" s="7">
         <v>148</v>
@@ -3729,7 +3733,7 @@
         <v>23</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O30" s="3" t="s">
         <v>25</v>
@@ -3738,7 +3742,7 @@
         <v>26</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="R30" s="8"/>
       <c r="S30" s="5"/>
@@ -3751,13 +3755,13 @@
         <v>16</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F31" s="9">
         <v>25</v>
@@ -3767,7 +3771,7 @@
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J31" s="7">
         <v>149</v>
@@ -3780,7 +3784,7 @@
         <v>23</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="O31" s="3" t="s">
         <v>25</v>
@@ -3789,7 +3793,7 @@
         <v>26</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="R31" s="8"/>
       <c r="S31" s="5"/>
@@ -3802,13 +3806,13 @@
         <v>16</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F32" s="9">
         <v>19</v>
@@ -3818,7 +3822,7 @@
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J32" s="7">
         <v>151</v>
@@ -3831,7 +3835,7 @@
         <v>23</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>25</v>
@@ -3840,7 +3844,7 @@
         <v>26</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="R32" s="8"/>
       <c r="S32" s="5"/>
@@ -3853,13 +3857,13 @@
         <v>16</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F33" s="7">
         <v>41</v>
@@ -3869,7 +3873,7 @@
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J33" s="7">
         <v>151</v>
@@ -3882,7 +3886,7 @@
         <v>23</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>25</v>
@@ -3891,7 +3895,7 @@
         <v>26</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="R33" s="8"/>
       <c r="S33" s="5"/>
@@ -3901,48 +3905,48 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="F34" s="9">
         <v>25</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J34" s="9">
         <v>14</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L34" s="7"/>
       <c r="M34" s="9" t="s">
         <v>23</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P34" s="7" t="s">
         <v>50</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="R34" s="8"/>
       <c r="S34" s="5"/>
@@ -3952,22 +3956,22 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="E35" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F35" s="9">
         <v>20</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H35" s="7"/>
       <c r="I35" s="3"/>
@@ -3975,23 +3979,23 @@
         <v>0</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L35" s="7"/>
       <c r="M35" s="7" t="s">
         <v>47</v>
       </c>
       <c r="N35" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P35" s="7" t="s">
         <v>50</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="R35" s="8"/>
       <c r="S35" s="5"/>
@@ -4001,22 +4005,22 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="E36" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F36" s="9">
         <v>20</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H36" s="7"/>
       <c r="I36" s="3"/>
@@ -4024,23 +4028,23 @@
         <v>0</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L36" s="7"/>
       <c r="M36" s="7" t="s">
         <v>47</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P36" s="7" t="s">
         <v>50</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="R36" s="8"/>
       <c r="S36" s="5"/>
@@ -4050,13 +4054,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>219</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>133</v>
@@ -4065,7 +4069,7 @@
         <v>21</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="3"/>
@@ -4073,23 +4077,23 @@
         <v>0</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L37" s="7"/>
       <c r="M37" s="7" t="s">
         <v>47</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P37" s="7" t="s">
         <v>50</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R37" s="8"/>
       <c r="S37" s="5"/>
@@ -4099,22 +4103,22 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="E38" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F38" s="9">
         <v>23</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="3"/>
@@ -4122,23 +4126,23 @@
         <v>0</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L38" s="7"/>
       <c r="M38" s="7" t="s">
         <v>47</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P38" s="7" t="s">
         <v>50</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="R38" s="8"/>
       <c r="S38" s="5"/>
@@ -4148,28 +4152,28 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F39" s="9">
         <v>70</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H39" s="10">
         <v>57</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="J39" s="7">
         <v>138</v>
@@ -4182,7 +4186,7 @@
         <v>47</v>
       </c>
       <c r="N39" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O39" s="3" t="s">
         <v>49</v>
@@ -4199,34 +4203,34 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F40" s="9">
         <v>76</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H40" s="10">
         <v>55</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="J40" s="9">
         <v>205</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L40" s="10">
         <v>142</v>
@@ -4235,7 +4239,7 @@
         <v>47</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O40" s="3" t="s">
         <v>49</v>
@@ -4252,28 +4256,28 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F41" s="9">
         <v>67</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H41" s="10">
         <v>58</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J41" s="9">
         <v>162</v>
@@ -4286,7 +4290,7 @@
         <v>47</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>49</v>
@@ -4303,28 +4307,28 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F42" s="9">
         <v>94</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H42" s="10">
         <v>54</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J42" s="9">
         <v>167</v>
@@ -4337,7 +4341,7 @@
         <v>47</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>49</v>
@@ -4354,28 +4358,28 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F43" s="9">
         <v>77</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H43" s="10">
         <v>55</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J43" s="9">
         <v>170</v>
@@ -4388,7 +4392,7 @@
         <v>47</v>
       </c>
       <c r="N43" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>49</v>
@@ -4405,28 +4409,28 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F44" s="9">
         <v>72</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H44" s="10">
         <v>56</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="J44" s="7">
         <v>158</v>
@@ -4439,7 +4443,7 @@
         <v>47</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>49</v>
@@ -4448,7 +4452,7 @@
         <v>50</v>
       </c>
       <c r="Q44" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="R44" s="8"/>
       <c r="S44" s="5"/>
@@ -4458,28 +4462,28 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F45" s="9">
         <v>81</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H45" s="10">
         <v>54</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J45" s="7">
         <v>137</v>
@@ -4492,7 +4496,7 @@
         <v>47</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>49</v>
@@ -4509,34 +4513,34 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F46" s="9">
         <v>89</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H46" s="10">
         <v>57</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="J46" s="9">
         <v>215</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L46" s="10">
         <v>136</v>
@@ -4545,7 +4549,7 @@
         <v>47</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>49</v>
@@ -4562,28 +4566,28 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F47" s="9">
         <v>95</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H47" s="10">
         <v>50</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J47" s="9">
         <v>182</v>
@@ -4596,7 +4600,7 @@
         <v>47</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>49</v>
@@ -4613,28 +4617,28 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F48" s="9">
         <v>77</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H48" s="10">
         <v>55</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="J48" s="7">
         <v>158</v>
@@ -4647,7 +4651,7 @@
         <v>47</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>49</v>
@@ -4664,34 +4668,34 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F49" s="9">
         <v>81</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H49" s="10">
         <v>53</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J49" s="9">
         <v>73</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L49" s="10">
         <v>140</v>
@@ -4700,7 +4704,7 @@
         <v>47</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>49</v>
@@ -4717,28 +4721,28 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F50" s="9">
         <v>80</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H50" s="10">
         <v>58</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J50" s="7">
         <v>150</v>
@@ -4751,7 +4755,7 @@
         <v>47</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O50" s="3" t="s">
         <v>49</v>
@@ -4768,28 +4772,28 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F51" s="9">
         <v>75</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H51" s="10">
         <v>50</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J51" s="7">
         <v>149</v>
@@ -4802,7 +4806,7 @@
         <v>47</v>
       </c>
       <c r="N51" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O51" s="3" t="s">
         <v>49</v>
@@ -4819,34 +4823,34 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F52" s="9">
         <v>78</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H52" s="10">
         <v>57</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J52" s="9">
         <v>105</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L52" s="10">
         <v>129</v>
@@ -4855,7 +4859,7 @@
         <v>47</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>49</v>
@@ -4872,28 +4876,28 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F53" s="9">
         <v>81</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H53" s="10">
         <v>52</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="J53" s="7">
         <v>154</v>
@@ -4906,7 +4910,7 @@
         <v>47</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O53" s="3" t="s">
         <v>49</v>
@@ -4923,34 +4927,34 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F54" s="9">
         <v>66</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H54" s="10">
         <v>48</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="J54" s="9">
         <v>324</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="L54" s="10">
         <v>137</v>
@@ -4959,7 +4963,7 @@
         <v>47</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>49</v>
@@ -4976,16 +4980,16 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>309</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>311</v>
       </c>
       <c r="F55" s="7">
         <v>60</v>
@@ -4995,13 +4999,13 @@
       </c>
       <c r="H55" s="7"/>
       <c r="I55" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="J55" s="9">
         <v>255</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="L55" s="10">
         <v>136</v>
@@ -5010,7 +5014,7 @@
         <v>47</v>
       </c>
       <c r="N55" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O55" s="3" t="s">
         <v>49</v>
@@ -5019,7 +5023,7 @@
         <v>50</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="R55" s="8"/>
       <c r="S55" s="5"/>
@@ -5029,34 +5033,34 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F56" s="9">
         <v>78</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H56" s="10">
         <v>59</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J56" s="9">
         <v>259</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="L56" s="10">
         <v>141</v>
@@ -5065,7 +5069,7 @@
         <v>47</v>
       </c>
       <c r="N56" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O56" s="3" t="s">
         <v>49</v>
@@ -5082,34 +5086,34 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F57" s="9">
         <v>82</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H57" s="10">
         <v>54</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="J57" s="9">
         <v>281</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="L57" s="10">
         <v>138</v>
@@ -5118,7 +5122,7 @@
         <v>47</v>
       </c>
       <c r="N57" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>49</v>
@@ -5135,28 +5139,28 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F58" s="9">
         <v>90</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H58" s="10">
         <v>53</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="J58" s="9">
         <v>192</v>
@@ -5169,7 +5173,7 @@
         <v>47</v>
       </c>
       <c r="N58" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>49</v>
@@ -5178,7 +5182,7 @@
         <v>50</v>
       </c>
       <c r="Q58" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="R58" s="8"/>
       <c r="S58" s="5"/>
@@ -5188,16 +5192,16 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F59" s="9">
         <v>65</v>
@@ -5207,13 +5211,13 @@
       </c>
       <c r="H59" s="7"/>
       <c r="I59" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J59" s="9">
         <v>215</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L59" s="10">
         <v>123</v>
@@ -5222,7 +5226,7 @@
         <v>47</v>
       </c>
       <c r="N59" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>49</v>
@@ -5239,28 +5243,28 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F60" s="9">
         <v>72</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H60" s="10">
         <v>57</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="J60" s="7">
         <v>153</v>
@@ -5273,7 +5277,7 @@
         <v>47</v>
       </c>
       <c r="N60" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>49</v>
@@ -5282,7 +5286,7 @@
         <v>50</v>
       </c>
       <c r="Q60" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="R60" s="8"/>
       <c r="S60" s="5"/>
@@ -5292,28 +5296,28 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F61" s="9">
         <v>80</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H61" s="10">
         <v>50</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="J61" s="9">
         <v>182</v>
@@ -5326,7 +5330,7 @@
         <v>47</v>
       </c>
       <c r="N61" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O61" s="3" t="s">
         <v>49</v>
@@ -5343,34 +5347,34 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F62" s="9">
         <v>67</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H62" s="10">
         <v>50</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="J62" s="9">
         <v>199</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="L62" s="10">
         <v>125</v>
@@ -5379,7 +5383,7 @@
         <v>47</v>
       </c>
       <c r="N62" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>49</v>
@@ -5396,34 +5400,34 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F63" s="9">
         <v>79</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H63" s="10">
         <v>51</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="J63" s="9">
         <v>182</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="L63" s="10">
         <v>137</v>
@@ -5432,7 +5436,7 @@
         <v>47</v>
       </c>
       <c r="N63" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O63" s="3" t="s">
         <v>49</v>
@@ -5441,7 +5445,7 @@
         <v>50</v>
       </c>
       <c r="Q63" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="R63" s="8"/>
       <c r="S63" s="5"/>
@@ -5451,28 +5455,28 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F64" s="9">
         <v>75</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H64" s="10">
         <v>57</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J64" s="7">
         <v>154</v>
@@ -5485,7 +5489,7 @@
         <v>47</v>
       </c>
       <c r="N64" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O64" s="3" t="s">
         <v>49</v>
@@ -5502,28 +5506,28 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F65" s="9">
         <v>76</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H65" s="10">
         <v>58</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="J65" s="7">
         <v>151</v>
@@ -5536,7 +5540,7 @@
         <v>47</v>
       </c>
       <c r="N65" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O65" s="3" t="s">
         <v>49</v>
@@ -5553,28 +5557,28 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F66" s="9">
         <v>67</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H66" s="10">
         <v>60</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J66" s="9">
         <v>188</v>
@@ -5587,7 +5591,7 @@
         <v>47</v>
       </c>
       <c r="N66" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>49</v>
@@ -5604,28 +5608,28 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F67" s="9">
         <v>67</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H67" s="10">
         <v>54</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="J67" s="7">
         <v>153</v>
@@ -5638,7 +5642,7 @@
         <v>47</v>
       </c>
       <c r="N67" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O67" s="3" t="s">
         <v>49</v>
@@ -5655,28 +5659,28 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F68" s="9">
         <v>68</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H68" s="10">
         <v>48</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="J68" s="7">
         <v>148</v>
@@ -5689,7 +5693,7 @@
         <v>47</v>
       </c>
       <c r="N68" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O68" s="3" t="s">
         <v>49</v>
@@ -5706,34 +5710,34 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F69" s="9">
         <v>91</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H69" s="10">
         <v>53</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="J69" s="9">
         <v>193</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="L69" s="10">
         <v>141</v>
@@ -5742,7 +5746,7 @@
         <v>47</v>
       </c>
       <c r="N69" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O69" s="3" t="s">
         <v>49</v>
@@ -5759,28 +5763,28 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F70" s="9">
         <v>122</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H70" s="10">
         <v>55</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J70" s="7">
         <v>135</v>
@@ -5793,7 +5797,7 @@
         <v>47</v>
       </c>
       <c r="N70" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O70" s="3" t="s">
         <v>49</v>
@@ -5802,7 +5806,7 @@
         <v>50</v>
       </c>
       <c r="Q70" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="R70" s="8"/>
       <c r="S70" s="5"/>
@@ -5812,34 +5816,34 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F71" s="9">
         <v>82</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H71" s="10">
         <v>58</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="J71" s="9">
         <v>180</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L71" s="10">
         <v>134</v>
@@ -5848,7 +5852,7 @@
         <v>47</v>
       </c>
       <c r="N71" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O71" s="3" t="s">
         <v>49</v>
@@ -5865,28 +5869,28 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F72" s="9">
         <v>88</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H72" s="10">
         <v>51</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J72" s="7">
         <v>148</v>
@@ -5899,7 +5903,7 @@
         <v>47</v>
       </c>
       <c r="N72" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>49</v>
@@ -5908,7 +5912,7 @@
         <v>50</v>
       </c>
       <c r="Q72" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="R72" s="8"/>
       <c r="S72" s="5"/>
@@ -5918,28 +5922,28 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F73" s="9">
         <v>114</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H73" s="10">
         <v>50</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="J73" s="7">
         <v>154</v>
@@ -5952,7 +5956,7 @@
         <v>47</v>
       </c>
       <c r="N73" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O73" s="3" t="s">
         <v>49</v>
@@ -5969,28 +5973,28 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F74" s="9">
         <v>90</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="H74" s="10">
         <v>58</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J74" s="7">
         <v>122</v>
@@ -6003,7 +6007,7 @@
         <v>47</v>
       </c>
       <c r="N74" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O74" s="3" t="s">
         <v>49</v>
@@ -6020,16 +6024,16 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F75" s="7">
         <v>51</v>
@@ -6039,13 +6043,13 @@
       </c>
       <c r="H75" s="7"/>
       <c r="I75" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="J75" s="9">
         <v>82</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="L75" s="10">
         <v>134</v>
@@ -6054,7 +6058,7 @@
         <v>47</v>
       </c>
       <c r="N75" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O75" s="3" t="s">
         <v>49</v>
@@ -6071,34 +6075,34 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F76" s="9">
         <v>95</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H76" s="10">
         <v>50</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J76" s="9">
         <v>89</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="L76" s="10">
         <v>138</v>
@@ -6107,7 +6111,7 @@
         <v>47</v>
       </c>
       <c r="N76" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>49</v>
@@ -6116,7 +6120,7 @@
         <v>50</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="R76" s="8"/>
       <c r="S76" s="5"/>
@@ -6126,34 +6130,34 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F77" s="9">
         <v>89</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H77" s="10">
         <v>53</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="J77" s="9">
         <v>77</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="L77" s="10">
         <v>128</v>
@@ -6162,7 +6166,7 @@
         <v>47</v>
       </c>
       <c r="N77" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O77" s="3" t="s">
         <v>49</v>
@@ -6179,16 +6183,16 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F78" s="7">
         <v>38</v>
@@ -6198,13 +6202,13 @@
       </c>
       <c r="H78" s="7"/>
       <c r="I78" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="J78" s="9">
         <v>49</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="L78" s="10">
         <v>121</v>
@@ -6213,7 +6217,7 @@
         <v>47</v>
       </c>
       <c r="N78" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O78" s="3" t="s">
         <v>49</v>
@@ -6230,34 +6234,34 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F79" s="9">
         <v>77</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H79" s="10">
         <v>55</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J79" s="9">
         <v>302</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="L79" s="10">
         <v>127</v>
@@ -6266,7 +6270,7 @@
         <v>47</v>
       </c>
       <c r="N79" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O79" s="3" t="s">
         <v>49</v>
@@ -6283,34 +6287,34 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F80" s="9">
         <v>87</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H80" s="10">
         <v>48</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="J80" s="9">
         <v>303</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L80" s="10">
         <v>127</v>
@@ -6319,7 +6323,7 @@
         <v>47</v>
       </c>
       <c r="N80" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O80" s="3" t="s">
         <v>49</v>
@@ -6336,34 +6340,34 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F81" s="9">
         <v>73</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H81" s="10">
         <v>52</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="J81" s="9">
         <v>214</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="L81" s="10">
         <v>132</v>
@@ -6372,7 +6376,7 @@
         <v>47</v>
       </c>
       <c r="N81" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>49</v>

--- a/marketing/auditorias-seo/revisao-titles-descriptions-h1-2026-09-25.xlsx
+++ b/marketing/auditorias-seo/revisao-titles-descriptions-h1-2026-09-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solveplan-my.sharepoint.com/personal/molina_solveplan_com/Documents/publica equipe/projetos/Pre Venda/Comercial/Marketing/1. MKT Estrategy/3. Agentes de IA/ccos-ratos/marketing/auditorias-seo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="6_{BDBA82EF-C4F1-454E-969C-820D58A5577D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDB42798-EB42-417A-AD2B-3EE58FA4EF94}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="6_{BDBA82EF-C4F1-454E-969C-820D58A5577D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC69FD2C-2CB4-4E11-A446-7EFDEB1DC238}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{B5D46161-3EB7-4448-AEF2-FB692F6EC46B}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="462">
   <si>
     <t>#</t>
   </si>
@@ -627,9 +627,6 @@
     <t>Acompanhamento de despesas com SAP | Solveplan</t>
   </si>
   <si>
-    <t>Mantenha o orçamento sob controle com inteligência, precisão e tecnologia de ponta. Com as soluções da Solveplan, você acompanha em tempo real o comparativo</t>
-  </si>
-  <si>
     <t>Compare orçado e realizado em tempo real com SAP Analytics Cloud. O acelerador da Solveplan dá controle das despesas com precisão.</t>
   </si>
   <si>
@@ -645,9 +642,6 @@
     <t>Política de Privacidade - Solveplan</t>
   </si>
   <si>
-    <t>A SOLVEPLAN compromete-se a proteger a privacidade de todos os dados/informações obtidos dos clientes, parceiros e fornecedores nos termos da Lei nº</t>
-  </si>
-  <si>
     <t>Trocar tag para H1: "Política de Privacidade"</t>
   </si>
   <si>
@@ -660,9 +654,6 @@
     <t>Termos de uso - Solveplan</t>
   </si>
   <si>
-    <t>A SOLVEPLAN declara que o tratamento de dados pessoais de clientes, parceiros, corpo de funcionário e prestadores de serviço durante e após a relação</t>
-  </si>
-  <si>
     <t>Trocar tag para H1: "Termos de Uso"</t>
   </si>
   <si>
@@ -672,9 +663,6 @@
     <t>Cookies - Solveplan</t>
   </si>
   <si>
-    <t>Um arquivo de texto que armazena informações como sua preferência de idioma para um site. Quando você visita o site novamente mais tarde, esse cookie é</t>
-  </si>
-  <si>
     <t>Trocar tag para H1: "Cookies"</t>
   </si>
   <si>
@@ -684,9 +672,6 @@
     <t>Responsabilidade e Disclosure - Solveplan</t>
   </si>
   <si>
-    <t>Na Solveplan, consideramos a segurança de nossos sistemas prioridade máxima. Não importa quanto estamos atentos com a segurança do sistema, ainda podem</t>
-  </si>
-  <si>
     <t>Trocar tag para H1 e corrigir: "Divulgação Responsavél" &gt; "Divulgação Responsável"</t>
   </si>
   <si>
@@ -1426,6 +1411,24 @@
   </si>
   <si>
     <t>Ganhe clareza total em tempo real. Com os dashboards da Solveplan, você transforma dados complexos em insights estratégicos, organizando KPIs e relatórios.</t>
+  </si>
+  <si>
+    <t>Mantenha o orçamento sob controle com inteligência, precisão e tecnologia de ponta. Com as soluções da Solveplan, você acompanha em tempo real</t>
+  </si>
+  <si>
+    <t>A SOLVEPLAN compromete-se a proteger a privacidade de todos os dados/informações obtidos dos clientes, parceiros e fornecedores nos termos da Lei</t>
+  </si>
+  <si>
+    <t>A SOLVEPLAN declara que o tratamento de dados pessoais de clientes, parceiros, corpo de funcionário e prestadores de serviço</t>
+  </si>
+  <si>
+    <t>Um arquivo de texto que armazena informações como sua preferência de idioma para um site.</t>
+  </si>
+  <si>
+    <t>Na Solveplan, consideramos a segurança de nossos sistemas prioridade máxima.</t>
+  </si>
+  <si>
+    <t>Não</t>
   </si>
 </sst>
 </file>
@@ -1927,12 +1930,12 @@
   <sheetData>
     <row r="1" spans="2:2" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B1" s="11" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" s="12" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
@@ -1940,32 +1943,32 @@
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" s="13" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" spans="2:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.3">
@@ -1973,27 +1976,27 @@
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
@@ -2001,22 +2004,22 @@
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.3">
@@ -2024,32 +2027,32 @@
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" s="13" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.3">
@@ -2057,7 +2060,7 @@
     </row>
     <row r="30" spans="2:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -2203,7 +2206,7 @@
         <v>27</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S2" s="5"/>
     </row>
@@ -2260,7 +2263,7 @@
         <v>34</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S3" s="5"/>
     </row>
@@ -2317,10 +2320,10 @@
         <v>42</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -2370,7 +2373,7 @@
         <v>51</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S5" s="5"/>
     </row>
@@ -2427,7 +2430,7 @@
         <v>58</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S6" s="5"/>
     </row>
@@ -2484,10 +2487,10 @@
         <v>65</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -2541,7 +2544,7 @@
       </c>
       <c r="Q8" s="3"/>
       <c r="R8" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S8" s="5"/>
     </row>
@@ -2594,7 +2597,7 @@
       </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S9" s="5"/>
     </row>
@@ -2649,7 +2652,7 @@
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S10" s="5"/>
     </row>
@@ -2706,7 +2709,7 @@
         <v>90</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S11" s="5"/>
     </row>
@@ -2763,7 +2766,7 @@
         <v>97</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S12" s="5"/>
     </row>
@@ -2820,7 +2823,7 @@
         <v>104</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S13" s="5"/>
     </row>
@@ -2875,7 +2878,7 @@
         <v>110</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S14" s="5"/>
     </row>
@@ -2932,7 +2935,7 @@
         <v>118</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S15" s="5"/>
     </row>
@@ -2989,7 +2992,7 @@
         <v>125</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S16" s="5"/>
     </row>
@@ -3042,7 +3045,7 @@
       </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S17" s="5"/>
     </row>
@@ -3099,7 +3102,7 @@
         <v>138</v>
       </c>
       <c r="R18" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S18" s="5"/>
     </row>
@@ -3154,7 +3157,7 @@
       </c>
       <c r="Q19" s="3"/>
       <c r="R19" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S19" s="5"/>
     </row>
@@ -3207,7 +3210,7 @@
       </c>
       <c r="Q20" s="3"/>
       <c r="R20" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S20" s="5"/>
     </row>
@@ -3262,7 +3265,7 @@
       </c>
       <c r="Q21" s="3"/>
       <c r="R21" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S21" s="5"/>
     </row>
@@ -3315,7 +3318,7 @@
       </c>
       <c r="Q22" s="3"/>
       <c r="R22" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S22" s="5"/>
     </row>
@@ -3368,7 +3371,7 @@
       </c>
       <c r="Q23" s="3"/>
       <c r="R23" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S23" s="5"/>
     </row>
@@ -3398,7 +3401,7 @@
         <v>56</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="J24" s="7">
         <v>156</v>
@@ -3423,7 +3426,7 @@
       </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S24" s="5"/>
     </row>
@@ -3476,7 +3479,7 @@
       </c>
       <c r="Q25" s="3"/>
       <c r="R25" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S25" s="5"/>
     </row>
@@ -3531,7 +3534,7 @@
       </c>
       <c r="Q26" s="3"/>
       <c r="R26" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S26" s="5"/>
     </row>
@@ -3561,7 +3564,7 @@
         <v>52</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="J27" s="7">
         <v>156</v>
@@ -3586,7 +3589,7 @@
       </c>
       <c r="Q27" s="3"/>
       <c r="R27" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S27" s="5"/>
     </row>
@@ -3616,7 +3619,7 @@
         <v>46</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="J28" s="7">
         <v>157</v>
@@ -3639,7 +3642,7 @@
       </c>
       <c r="Q28" s="3"/>
       <c r="R28" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="S28" s="5"/>
     </row>
@@ -3669,13 +3672,13 @@
         <v>46</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>194</v>
+        <v>456</v>
       </c>
       <c r="J29" s="7">
         <v>156</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L29" s="10">
         <v>130</v>
@@ -3684,7 +3687,7 @@
         <v>23</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>25</v>
@@ -3693,7 +3696,9 @@
         <v>26</v>
       </c>
       <c r="Q29" s="3"/>
-      <c r="R29" s="8"/>
+      <c r="R29" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S29" s="5"/>
     </row>
     <row r="30" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -3704,13 +3709,13 @@
         <v>16</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="F30" s="7">
         <v>35</v>
@@ -3720,7 +3725,7 @@
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="3" t="s">
-        <v>200</v>
+        <v>457</v>
       </c>
       <c r="J30" s="7">
         <v>148</v>
@@ -3733,7 +3738,7 @@
         <v>23</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="O30" s="3" t="s">
         <v>25</v>
@@ -3742,9 +3747,11 @@
         <v>26</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="R30" s="8"/>
+        <v>200</v>
+      </c>
+      <c r="R30" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S30" s="5"/>
     </row>
     <row r="31" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -3755,13 +3762,13 @@
         <v>16</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F31" s="9">
         <v>25</v>
@@ -3771,7 +3778,7 @@
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="3" t="s">
-        <v>205</v>
+        <v>458</v>
       </c>
       <c r="J31" s="7">
         <v>149</v>
@@ -3784,7 +3791,7 @@
         <v>23</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O31" s="3" t="s">
         <v>25</v>
@@ -3793,9 +3800,11 @@
         <v>26</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="R31" s="8"/>
+        <v>200</v>
+      </c>
+      <c r="R31" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S31" s="5"/>
     </row>
     <row r="32" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -3806,13 +3815,13 @@
         <v>16</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F32" s="9">
         <v>19</v>
@@ -3822,7 +3831,7 @@
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="3" t="s">
-        <v>209</v>
+        <v>459</v>
       </c>
       <c r="J32" s="7">
         <v>151</v>
@@ -3835,7 +3844,7 @@
         <v>23</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>25</v>
@@ -3844,9 +3853,11 @@
         <v>26</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="R32" s="8"/>
+        <v>200</v>
+      </c>
+      <c r="R32" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S32" s="5"/>
     </row>
     <row r="33" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -3857,13 +3868,13 @@
         <v>16</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F33" s="7">
         <v>41</v>
@@ -3873,7 +3884,7 @@
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="3" t="s">
-        <v>213</v>
+        <v>460</v>
       </c>
       <c r="J33" s="7">
         <v>151</v>
@@ -3886,7 +3897,7 @@
         <v>23</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>25</v>
@@ -3895,9 +3906,11 @@
         <v>26</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="R33" s="8"/>
+        <v>200</v>
+      </c>
+      <c r="R33" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S33" s="5"/>
     </row>
     <row r="34" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -3905,48 +3918,48 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F34" s="9">
         <v>25</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="J34" s="9">
         <v>14</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="L34" s="7"/>
       <c r="M34" s="9" t="s">
         <v>23</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="P34" s="7" t="s">
         <v>50</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="R34" s="8"/>
       <c r="S34" s="5"/>
@@ -3956,22 +3969,22 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F35" s="9">
         <v>20</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="H35" s="7"/>
       <c r="I35" s="3"/>
@@ -3979,23 +3992,23 @@
         <v>0</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="L35" s="7"/>
       <c r="M35" s="7" t="s">
         <v>47</v>
       </c>
       <c r="N35" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="P35" s="7" t="s">
         <v>50</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="R35" s="8"/>
       <c r="S35" s="5"/>
@@ -4005,22 +4018,22 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F36" s="9">
         <v>20</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="H36" s="7"/>
       <c r="I36" s="3"/>
@@ -4028,23 +4041,23 @@
         <v>0</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="L36" s="7"/>
       <c r="M36" s="7" t="s">
         <v>47</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="P36" s="7" t="s">
         <v>50</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="R36" s="8"/>
       <c r="S36" s="5"/>
@@ -4054,13 +4067,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>133</v>
@@ -4069,7 +4082,7 @@
         <v>21</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="3"/>
@@ -4077,23 +4090,23 @@
         <v>0</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="L37" s="7"/>
       <c r="M37" s="7" t="s">
         <v>47</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="P37" s="7" t="s">
         <v>50</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="R37" s="8"/>
       <c r="S37" s="5"/>
@@ -4103,22 +4116,22 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="F38" s="9">
         <v>23</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="3"/>
@@ -4126,23 +4139,23 @@
         <v>0</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="L38" s="7"/>
       <c r="M38" s="7" t="s">
         <v>47</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="P38" s="7" t="s">
         <v>50</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="R38" s="8"/>
       <c r="S38" s="5"/>
@@ -4152,28 +4165,28 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F39" s="9">
         <v>70</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="H39" s="10">
         <v>57</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="J39" s="7">
         <v>138</v>
@@ -4186,7 +4199,7 @@
         <v>47</v>
       </c>
       <c r="N39" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O39" s="3" t="s">
         <v>49</v>
@@ -4195,7 +4208,9 @@
         <v>50</v>
       </c>
       <c r="Q39" s="3"/>
-      <c r="R39" s="8"/>
+      <c r="R39" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S39" s="5"/>
     </row>
     <row r="40" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -4203,34 +4218,34 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F40" s="9">
         <v>76</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="H40" s="10">
         <v>55</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="J40" s="9">
         <v>205</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="L40" s="10">
         <v>142</v>
@@ -4239,7 +4254,7 @@
         <v>47</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O40" s="3" t="s">
         <v>49</v>
@@ -4248,7 +4263,9 @@
         <v>50</v>
       </c>
       <c r="Q40" s="3"/>
-      <c r="R40" s="8"/>
+      <c r="R40" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S40" s="5"/>
     </row>
     <row r="41" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -4256,28 +4273,28 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="F41" s="9">
         <v>67</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H41" s="10">
         <v>58</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="J41" s="9">
         <v>162</v>
@@ -4290,7 +4307,7 @@
         <v>47</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>49</v>
@@ -4299,7 +4316,9 @@
         <v>50</v>
       </c>
       <c r="Q41" s="3"/>
-      <c r="R41" s="8"/>
+      <c r="R41" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S41" s="5"/>
     </row>
     <row r="42" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -4307,28 +4326,28 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F42" s="9">
         <v>94</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="H42" s="10">
         <v>54</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="J42" s="9">
         <v>167</v>
@@ -4341,7 +4360,7 @@
         <v>47</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>49</v>
@@ -4350,7 +4369,9 @@
         <v>50</v>
       </c>
       <c r="Q42" s="3"/>
-      <c r="R42" s="8"/>
+      <c r="R42" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S42" s="5"/>
     </row>
     <row r="43" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -4358,28 +4379,28 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F43" s="9">
         <v>77</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="H43" s="10">
         <v>55</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="J43" s="9">
         <v>170</v>
@@ -4392,7 +4413,7 @@
         <v>47</v>
       </c>
       <c r="N43" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>49</v>
@@ -4401,7 +4422,9 @@
         <v>50</v>
       </c>
       <c r="Q43" s="3"/>
-      <c r="R43" s="8"/>
+      <c r="R43" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S43" s="5"/>
     </row>
     <row r="44" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -4409,28 +4432,28 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F44" s="9">
         <v>72</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="H44" s="10">
         <v>56</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="J44" s="7">
         <v>158</v>
@@ -4443,7 +4466,7 @@
         <v>47</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>49</v>
@@ -4452,9 +4475,11 @@
         <v>50</v>
       </c>
       <c r="Q44" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="R44" s="8"/>
+        <v>257</v>
+      </c>
+      <c r="R44" s="8" t="s">
+        <v>461</v>
+      </c>
       <c r="S44" s="5"/>
     </row>
     <row r="45" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -4462,28 +4487,28 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="F45" s="9">
         <v>81</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="H45" s="10">
         <v>54</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="J45" s="7">
         <v>137</v>
@@ -4496,7 +4521,7 @@
         <v>47</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>49</v>
@@ -4505,7 +4530,9 @@
         <v>50</v>
       </c>
       <c r="Q45" s="3"/>
-      <c r="R45" s="8"/>
+      <c r="R45" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S45" s="5"/>
     </row>
     <row r="46" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -4513,34 +4540,34 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="F46" s="9">
         <v>89</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="H46" s="10">
         <v>57</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="J46" s="9">
         <v>215</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="L46" s="10">
         <v>136</v>
@@ -4549,7 +4576,7 @@
         <v>47</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>49</v>
@@ -4558,7 +4585,9 @@
         <v>50</v>
       </c>
       <c r="Q46" s="3"/>
-      <c r="R46" s="8"/>
+      <c r="R46" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S46" s="5"/>
     </row>
     <row r="47" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -4566,28 +4595,28 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F47" s="9">
         <v>95</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="H47" s="10">
         <v>50</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="J47" s="9">
         <v>182</v>
@@ -4600,7 +4629,7 @@
         <v>47</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>49</v>
@@ -4609,7 +4638,9 @@
         <v>50</v>
       </c>
       <c r="Q47" s="3"/>
-      <c r="R47" s="8"/>
+      <c r="R47" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S47" s="5"/>
     </row>
     <row r="48" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -4617,28 +4648,28 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F48" s="9">
         <v>77</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="H48" s="10">
         <v>55</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="J48" s="7">
         <v>158</v>
@@ -4651,7 +4682,7 @@
         <v>47</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>49</v>
@@ -4660,7 +4691,9 @@
         <v>50</v>
       </c>
       <c r="Q48" s="3"/>
-      <c r="R48" s="8"/>
+      <c r="R48" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S48" s="5"/>
     </row>
     <row r="49" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -4668,34 +4701,34 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F49" s="9">
         <v>81</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="H49" s="10">
         <v>53</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="J49" s="9">
         <v>73</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="L49" s="10">
         <v>140</v>
@@ -4704,7 +4737,7 @@
         <v>47</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>49</v>
@@ -4713,7 +4746,9 @@
         <v>50</v>
       </c>
       <c r="Q49" s="3"/>
-      <c r="R49" s="8"/>
+      <c r="R49" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S49" s="5"/>
     </row>
     <row r="50" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -4721,28 +4756,28 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F50" s="9">
         <v>80</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="H50" s="10">
         <v>58</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="J50" s="7">
         <v>150</v>
@@ -4755,7 +4790,7 @@
         <v>47</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O50" s="3" t="s">
         <v>49</v>
@@ -4764,7 +4799,9 @@
         <v>50</v>
       </c>
       <c r="Q50" s="3"/>
-      <c r="R50" s="8"/>
+      <c r="R50" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S50" s="5"/>
     </row>
     <row r="51" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -4772,28 +4809,28 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="F51" s="9">
         <v>75</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="H51" s="10">
         <v>50</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="J51" s="7">
         <v>149</v>
@@ -4806,7 +4843,7 @@
         <v>47</v>
       </c>
       <c r="N51" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O51" s="3" t="s">
         <v>49</v>
@@ -4815,7 +4852,9 @@
         <v>50</v>
       </c>
       <c r="Q51" s="3"/>
-      <c r="R51" s="8"/>
+      <c r="R51" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S51" s="5"/>
     </row>
     <row r="52" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -4823,34 +4862,34 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="F52" s="9">
         <v>78</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="H52" s="10">
         <v>57</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="J52" s="9">
         <v>105</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="L52" s="10">
         <v>129</v>
@@ -4859,7 +4898,7 @@
         <v>47</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>49</v>
@@ -4868,7 +4907,9 @@
         <v>50</v>
       </c>
       <c r="Q52" s="3"/>
-      <c r="R52" s="8"/>
+      <c r="R52" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S52" s="5"/>
     </row>
     <row r="53" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -4876,28 +4917,28 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="F53" s="9">
         <v>81</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="H53" s="10">
         <v>52</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="J53" s="7">
         <v>154</v>
@@ -4910,7 +4951,7 @@
         <v>47</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O53" s="3" t="s">
         <v>49</v>
@@ -4919,7 +4960,9 @@
         <v>50</v>
       </c>
       <c r="Q53" s="3"/>
-      <c r="R53" s="8"/>
+      <c r="R53" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S53" s="5"/>
     </row>
     <row r="54" spans="1:19" ht="86.4" x14ac:dyDescent="0.3">
@@ -4927,34 +4970,34 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="F54" s="9">
         <v>66</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="H54" s="10">
         <v>48</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="J54" s="9">
         <v>324</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="L54" s="10">
         <v>137</v>
@@ -4963,7 +5006,7 @@
         <v>47</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>49</v>
@@ -4972,7 +5015,9 @@
         <v>50</v>
       </c>
       <c r="Q54" s="3"/>
-      <c r="R54" s="8"/>
+      <c r="R54" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S54" s="5"/>
     </row>
     <row r="55" spans="1:19" ht="72" x14ac:dyDescent="0.3">
@@ -4980,16 +5025,16 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="F55" s="7">
         <v>60</v>
@@ -4999,13 +5044,13 @@
       </c>
       <c r="H55" s="7"/>
       <c r="I55" s="3" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="J55" s="9">
         <v>255</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="L55" s="10">
         <v>136</v>
@@ -5014,7 +5059,7 @@
         <v>47</v>
       </c>
       <c r="N55" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O55" s="3" t="s">
         <v>49</v>
@@ -5023,9 +5068,11 @@
         <v>50</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="R55" s="8"/>
+        <v>307</v>
+      </c>
+      <c r="R55" s="8" t="s">
+        <v>461</v>
+      </c>
       <c r="S55" s="5"/>
     </row>
     <row r="56" spans="1:19" ht="72" x14ac:dyDescent="0.3">
@@ -5033,34 +5080,34 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F56" s="9">
         <v>78</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="H56" s="10">
         <v>59</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="J56" s="9">
         <v>259</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="L56" s="10">
         <v>141</v>
@@ -5069,7 +5116,7 @@
         <v>47</v>
       </c>
       <c r="N56" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O56" s="3" t="s">
         <v>49</v>
@@ -5078,7 +5125,9 @@
         <v>50</v>
       </c>
       <c r="Q56" s="3"/>
-      <c r="R56" s="8"/>
+      <c r="R56" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S56" s="5"/>
     </row>
     <row r="57" spans="1:19" ht="72" x14ac:dyDescent="0.3">
@@ -5086,34 +5135,34 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="F57" s="9">
         <v>82</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="H57" s="10">
         <v>54</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="J57" s="9">
         <v>281</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="L57" s="10">
         <v>138</v>
@@ -5122,7 +5171,7 @@
         <v>47</v>
       </c>
       <c r="N57" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>49</v>
@@ -5131,7 +5180,9 @@
         <v>50</v>
       </c>
       <c r="Q57" s="3"/>
-      <c r="R57" s="8"/>
+      <c r="R57" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S57" s="5"/>
     </row>
     <row r="58" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -5139,28 +5190,28 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F58" s="9">
         <v>90</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="H58" s="10">
         <v>53</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="J58" s="9">
         <v>192</v>
@@ -5173,7 +5224,7 @@
         <v>47</v>
       </c>
       <c r="N58" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>49</v>
@@ -5182,9 +5233,11 @@
         <v>50</v>
       </c>
       <c r="Q58" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="R58" s="8"/>
+        <v>322</v>
+      </c>
+      <c r="R58" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S58" s="5"/>
     </row>
     <row r="59" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -5192,16 +5245,16 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="F59" s="9">
         <v>65</v>
@@ -5211,13 +5264,13 @@
       </c>
       <c r="H59" s="7"/>
       <c r="I59" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="J59" s="9">
         <v>215</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="L59" s="10">
         <v>123</v>
@@ -5226,7 +5279,7 @@
         <v>47</v>
       </c>
       <c r="N59" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>49</v>
@@ -5235,7 +5288,9 @@
         <v>50</v>
       </c>
       <c r="Q59" s="3"/>
-      <c r="R59" s="8"/>
+      <c r="R59" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S59" s="5"/>
     </row>
     <row r="60" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -5243,28 +5298,28 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="F60" s="9">
         <v>72</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="H60" s="10">
         <v>57</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="J60" s="7">
         <v>153</v>
@@ -5277,7 +5332,7 @@
         <v>47</v>
       </c>
       <c r="N60" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>49</v>
@@ -5286,9 +5341,11 @@
         <v>50</v>
       </c>
       <c r="Q60" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="R60" s="8"/>
+        <v>307</v>
+      </c>
+      <c r="R60" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S60" s="5"/>
     </row>
     <row r="61" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -5296,28 +5353,28 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="F61" s="9">
         <v>80</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="H61" s="10">
         <v>50</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="J61" s="9">
         <v>182</v>
@@ -5330,7 +5387,7 @@
         <v>47</v>
       </c>
       <c r="N61" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O61" s="3" t="s">
         <v>49</v>
@@ -5339,7 +5396,9 @@
         <v>50</v>
       </c>
       <c r="Q61" s="3"/>
-      <c r="R61" s="8"/>
+      <c r="R61" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S61" s="5"/>
     </row>
     <row r="62" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -5347,34 +5406,34 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="F62" s="9">
         <v>67</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="H62" s="10">
         <v>50</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="J62" s="9">
         <v>199</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="L62" s="10">
         <v>125</v>
@@ -5383,7 +5442,7 @@
         <v>47</v>
       </c>
       <c r="N62" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>49</v>
@@ -5392,7 +5451,9 @@
         <v>50</v>
       </c>
       <c r="Q62" s="3"/>
-      <c r="R62" s="8"/>
+      <c r="R62" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S62" s="5"/>
     </row>
     <row r="63" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -5400,34 +5461,34 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="F63" s="9">
         <v>79</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="H63" s="10">
         <v>51</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="J63" s="9">
         <v>182</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="L63" s="10">
         <v>137</v>
@@ -5436,7 +5497,7 @@
         <v>47</v>
       </c>
       <c r="N63" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O63" s="3" t="s">
         <v>49</v>
@@ -5445,9 +5506,11 @@
         <v>50</v>
       </c>
       <c r="Q63" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="R63" s="8"/>
+        <v>344</v>
+      </c>
+      <c r="R63" s="8" t="s">
+        <v>461</v>
+      </c>
       <c r="S63" s="5"/>
     </row>
     <row r="64" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -5455,28 +5518,28 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="F64" s="9">
         <v>75</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="H64" s="10">
         <v>57</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="J64" s="7">
         <v>154</v>
@@ -5489,7 +5552,7 @@
         <v>47</v>
       </c>
       <c r="N64" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O64" s="3" t="s">
         <v>49</v>
@@ -5498,7 +5561,9 @@
         <v>50</v>
       </c>
       <c r="Q64" s="3"/>
-      <c r="R64" s="8"/>
+      <c r="R64" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S64" s="5"/>
     </row>
     <row r="65" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -5506,28 +5571,28 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="F65" s="9">
         <v>76</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="H65" s="10">
         <v>58</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="J65" s="7">
         <v>151</v>
@@ -5540,7 +5605,7 @@
         <v>47</v>
       </c>
       <c r="N65" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O65" s="3" t="s">
         <v>49</v>
@@ -5549,7 +5614,9 @@
         <v>50</v>
       </c>
       <c r="Q65" s="3"/>
-      <c r="R65" s="8"/>
+      <c r="R65" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S65" s="5"/>
     </row>
     <row r="66" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -5557,28 +5624,28 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="F66" s="9">
         <v>67</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="H66" s="10">
         <v>60</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="J66" s="9">
         <v>188</v>
@@ -5591,7 +5658,7 @@
         <v>47</v>
       </c>
       <c r="N66" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>49</v>
@@ -5600,7 +5667,9 @@
         <v>50</v>
       </c>
       <c r="Q66" s="3"/>
-      <c r="R66" s="8"/>
+      <c r="R66" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S66" s="5"/>
     </row>
     <row r="67" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -5608,28 +5677,28 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="F67" s="9">
         <v>67</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="H67" s="10">
         <v>54</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J67" s="7">
         <v>153</v>
@@ -5642,7 +5711,7 @@
         <v>47</v>
       </c>
       <c r="N67" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O67" s="3" t="s">
         <v>49</v>
@@ -5651,7 +5720,9 @@
         <v>50</v>
       </c>
       <c r="Q67" s="3"/>
-      <c r="R67" s="8"/>
+      <c r="R67" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S67" s="5"/>
     </row>
     <row r="68" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -5659,28 +5730,28 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F68" s="9">
         <v>68</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H68" s="10">
         <v>48</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="J68" s="7">
         <v>148</v>
@@ -5693,7 +5764,7 @@
         <v>47</v>
       </c>
       <c r="N68" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O68" s="3" t="s">
         <v>49</v>
@@ -5702,7 +5773,9 @@
         <v>50</v>
       </c>
       <c r="Q68" s="3"/>
-      <c r="R68" s="8"/>
+      <c r="R68" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S68" s="5"/>
     </row>
     <row r="69" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -5710,34 +5783,34 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="F69" s="9">
         <v>91</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="H69" s="10">
         <v>53</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="J69" s="9">
         <v>193</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="L69" s="10">
         <v>141</v>
@@ -5746,7 +5819,7 @@
         <v>47</v>
       </c>
       <c r="N69" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O69" s="3" t="s">
         <v>49</v>
@@ -5755,7 +5828,9 @@
         <v>50</v>
       </c>
       <c r="Q69" s="3"/>
-      <c r="R69" s="8"/>
+      <c r="R69" s="8" t="s">
+        <v>461</v>
+      </c>
       <c r="S69" s="5"/>
     </row>
     <row r="70" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -5763,28 +5838,28 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="F70" s="9">
         <v>122</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="H70" s="10">
         <v>55</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="J70" s="7">
         <v>135</v>
@@ -5797,7 +5872,7 @@
         <v>47</v>
       </c>
       <c r="N70" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O70" s="3" t="s">
         <v>49</v>
@@ -5806,9 +5881,11 @@
         <v>50</v>
       </c>
       <c r="Q70" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="R70" s="8"/>
+        <v>374</v>
+      </c>
+      <c r="R70" s="8" t="s">
+        <v>461</v>
+      </c>
       <c r="S70" s="5"/>
     </row>
     <row r="71" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -5816,34 +5893,34 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F71" s="9">
         <v>82</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="H71" s="10">
         <v>58</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="J71" s="9">
         <v>180</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="L71" s="10">
         <v>134</v>
@@ -5852,7 +5929,7 @@
         <v>47</v>
       </c>
       <c r="N71" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O71" s="3" t="s">
         <v>49</v>
@@ -5861,7 +5938,9 @@
         <v>50</v>
       </c>
       <c r="Q71" s="3"/>
-      <c r="R71" s="8"/>
+      <c r="R71" s="8" t="s">
+        <v>461</v>
+      </c>
       <c r="S71" s="5"/>
     </row>
     <row r="72" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -5869,28 +5948,28 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="F72" s="9">
         <v>88</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="H72" s="10">
         <v>51</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="J72" s="7">
         <v>148</v>
@@ -5903,7 +5982,7 @@
         <v>47</v>
       </c>
       <c r="N72" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>49</v>
@@ -5912,7 +5991,7 @@
         <v>50</v>
       </c>
       <c r="Q72" s="3" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="R72" s="8"/>
       <c r="S72" s="5"/>
@@ -5922,28 +6001,28 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="F73" s="9">
         <v>114</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="H73" s="10">
         <v>50</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="J73" s="7">
         <v>154</v>
@@ -5956,7 +6035,7 @@
         <v>47</v>
       </c>
       <c r="N73" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O73" s="3" t="s">
         <v>49</v>
@@ -5973,28 +6052,28 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>127</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="F74" s="9">
         <v>90</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="H74" s="10">
         <v>58</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="J74" s="7">
         <v>122</v>
@@ -6007,7 +6086,7 @@
         <v>47</v>
       </c>
       <c r="N74" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O74" s="3" t="s">
         <v>49</v>
@@ -6024,16 +6103,16 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="F75" s="7">
         <v>51</v>
@@ -6043,13 +6122,13 @@
       </c>
       <c r="H75" s="7"/>
       <c r="I75" s="3" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="J75" s="9">
         <v>82</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="L75" s="10">
         <v>134</v>
@@ -6058,7 +6137,7 @@
         <v>47</v>
       </c>
       <c r="N75" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O75" s="3" t="s">
         <v>49</v>
@@ -6075,34 +6154,34 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="F76" s="9">
         <v>95</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="H76" s="10">
         <v>50</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="J76" s="9">
         <v>89</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="L76" s="10">
         <v>138</v>
@@ -6111,7 +6190,7 @@
         <v>47</v>
       </c>
       <c r="N76" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>49</v>
@@ -6120,7 +6199,7 @@
         <v>50</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="R76" s="8"/>
       <c r="S76" s="5"/>
@@ -6130,34 +6209,34 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="F77" s="9">
         <v>89</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H77" s="10">
         <v>53</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="J77" s="9">
         <v>77</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="L77" s="10">
         <v>128</v>
@@ -6166,7 +6245,7 @@
         <v>47</v>
       </c>
       <c r="N77" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O77" s="3" t="s">
         <v>49</v>
@@ -6183,16 +6262,16 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="F78" s="7">
         <v>38</v>
@@ -6202,13 +6281,13 @@
       </c>
       <c r="H78" s="7"/>
       <c r="I78" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="J78" s="9">
         <v>49</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="L78" s="10">
         <v>121</v>
@@ -6217,7 +6296,7 @@
         <v>47</v>
       </c>
       <c r="N78" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O78" s="3" t="s">
         <v>49</v>
@@ -6234,34 +6313,34 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="F79" s="9">
         <v>77</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H79" s="10">
         <v>55</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="J79" s="9">
         <v>302</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="L79" s="10">
         <v>127</v>
@@ -6270,7 +6349,7 @@
         <v>47</v>
       </c>
       <c r="N79" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O79" s="3" t="s">
         <v>49</v>
@@ -6287,34 +6366,34 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="F80" s="9">
         <v>87</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="H80" s="10">
         <v>48</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="J80" s="9">
         <v>303</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L80" s="10">
         <v>127</v>
@@ -6323,7 +6402,7 @@
         <v>47</v>
       </c>
       <c r="N80" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O80" s="3" t="s">
         <v>49</v>
@@ -6340,34 +6419,34 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="F81" s="9">
         <v>73</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="H81" s="10">
         <v>52</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="J81" s="9">
         <v>214</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="L81" s="10">
         <v>132</v>
@@ -6376,7 +6455,7 @@
         <v>47</v>
       </c>
       <c r="N81" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>49</v>

--- a/marketing/auditorias-seo/revisao-titles-descriptions-h1-2026-09-25.xlsx
+++ b/marketing/auditorias-seo/revisao-titles-descriptions-h1-2026-09-25.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solveplan-my.sharepoint.com/personal/molina_solveplan_com/Documents/publica equipe/projetos/Pre Venda/Comercial/Marketing/1. MKT Estrategy/3. Agentes de IA/ccos-ratos/marketing/auditorias-seo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\AppData\Local\Temp\claude\c--Users-franc-solveplan-com-Roberto-Molina---Marketing-1--MKT-Estrategy-3--Agentes-de-IA-ccos-ratos\3fe7c38d-8aa5-4234-b9e2-eb8021efc363\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="6_{BDBA82EF-C4F1-454E-969C-820D58A5577D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC69FD2C-2CB4-4E11-A446-7EFDEB1DC238}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DE3927-6640-4E47-A70F-3B14CD9D8560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{B5D46161-3EB7-4448-AEF2-FB692F6EC46B}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="463">
   <si>
     <t>#</t>
   </si>
@@ -1398,9 +1398,6 @@
     <t>Sim</t>
   </si>
   <si>
-    <t>A pagina não é para publicar, deixa em draft</t>
-  </si>
-  <si>
     <t>Só title e description. H1 fica para o rascunho (muda o visual)</t>
   </si>
   <si>
@@ -1429,6 +1426,12 @@
   </si>
   <si>
     <t>Não</t>
+  </si>
+  <si>
+    <t>Rascunho</t>
+  </si>
+  <si>
+    <t>Rascunho + 301 para /contato/; tirar card de /servicos/ no rascunho</t>
   </si>
 </sst>
 </file>
@@ -2323,7 +2326,7 @@
         <v>450</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -2487,10 +2490,10 @@
         <v>65</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -3401,7 +3404,7 @@
         <v>56</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="J24" s="7">
         <v>156</v>
@@ -3564,7 +3567,7 @@
         <v>52</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J27" s="7">
         <v>156</v>
@@ -3619,7 +3622,7 @@
         <v>46</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="J28" s="7">
         <v>157</v>
@@ -3672,7 +3675,7 @@
         <v>46</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="J29" s="7">
         <v>156</v>
@@ -3725,7 +3728,7 @@
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J30" s="7">
         <v>148</v>
@@ -3778,7 +3781,7 @@
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J31" s="7">
         <v>149</v>
@@ -3831,7 +3834,7 @@
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J32" s="7">
         <v>151</v>
@@ -3884,7 +3887,7 @@
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J33" s="7">
         <v>151</v>
@@ -3961,7 +3964,9 @@
       <c r="Q34" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="R34" s="8"/>
+      <c r="R34" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S34" s="5"/>
     </row>
     <row r="35" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -4010,7 +4015,9 @@
       <c r="Q35" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="R35" s="8"/>
+      <c r="R35" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S35" s="5"/>
     </row>
     <row r="36" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -4059,7 +4066,9 @@
       <c r="Q36" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="R36" s="8"/>
+      <c r="R36" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S36" s="5"/>
     </row>
     <row r="37" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -4108,7 +4117,9 @@
       <c r="Q37" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="R37" s="8"/>
+      <c r="R37" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S37" s="5"/>
     </row>
     <row r="38" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
@@ -4157,7 +4168,9 @@
       <c r="Q38" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="R38" s="8"/>
+      <c r="R38" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S38" s="5"/>
     </row>
     <row r="39" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -4478,7 +4491,7 @@
         <v>257</v>
       </c>
       <c r="R44" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="S44" s="5"/>
     </row>
@@ -5071,7 +5084,7 @@
         <v>307</v>
       </c>
       <c r="R55" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="S55" s="5"/>
     </row>
@@ -5509,7 +5522,7 @@
         <v>344</v>
       </c>
       <c r="R63" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="S63" s="5"/>
     </row>
@@ -5829,7 +5842,7 @@
       </c>
       <c r="Q69" s="3"/>
       <c r="R69" s="8" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="S69" s="5"/>
     </row>
@@ -5884,7 +5897,7 @@
         <v>374</v>
       </c>
       <c r="R70" s="8" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="S70" s="5"/>
     </row>
@@ -5939,7 +5952,7 @@
       </c>
       <c r="Q71" s="3"/>
       <c r="R71" s="8" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="S71" s="5"/>
     </row>
@@ -5993,7 +6006,9 @@
       <c r="Q72" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="R72" s="8"/>
+      <c r="R72" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S72" s="5"/>
     </row>
     <row r="73" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -6044,7 +6059,9 @@
         <v>50</v>
       </c>
       <c r="Q73" s="3"/>
-      <c r="R73" s="8"/>
+      <c r="R73" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S73" s="5"/>
     </row>
     <row r="74" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -6095,7 +6112,9 @@
         <v>50</v>
       </c>
       <c r="Q74" s="3"/>
-      <c r="R74" s="8"/>
+      <c r="R74" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S74" s="5"/>
     </row>
     <row r="75" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -6146,7 +6165,9 @@
         <v>50</v>
       </c>
       <c r="Q75" s="3"/>
-      <c r="R75" s="8"/>
+      <c r="R75" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S75" s="5"/>
     </row>
     <row r="76" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -6201,7 +6222,9 @@
       <c r="Q76" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="R76" s="8"/>
+      <c r="R76" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S76" s="5"/>
     </row>
     <row r="77" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -6254,7 +6277,9 @@
         <v>50</v>
       </c>
       <c r="Q77" s="3"/>
-      <c r="R77" s="8"/>
+      <c r="R77" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S77" s="5"/>
     </row>
     <row r="78" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -6305,7 +6330,9 @@
         <v>50</v>
       </c>
       <c r="Q78" s="3"/>
-      <c r="R78" s="8"/>
+      <c r="R78" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S78" s="5"/>
     </row>
     <row r="79" spans="1:19" ht="86.4" x14ac:dyDescent="0.3">
@@ -6358,7 +6385,9 @@
         <v>50</v>
       </c>
       <c r="Q79" s="3"/>
-      <c r="R79" s="8"/>
+      <c r="R79" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S79" s="5"/>
     </row>
     <row r="80" spans="1:19" ht="86.4" x14ac:dyDescent="0.3">
@@ -6411,7 +6440,9 @@
         <v>50</v>
       </c>
       <c r="Q80" s="3"/>
-      <c r="R80" s="8"/>
+      <c r="R80" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S80" s="5"/>
     </row>
     <row r="81" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
@@ -6464,7 +6495,9 @@
         <v>50</v>
       </c>
       <c r="Q81" s="3"/>
-      <c r="R81" s="8"/>
+      <c r="R81" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="S81" s="5"/>
     </row>
   </sheetData>
